--- a/healthcare_forms/047_speech_language_pathology_supervision_log--healthcare_forms.xlsx
+++ b/healthcare_forms/047_speech_language_pathology_supervision_log--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -561,23 +561,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>activities</t>
+          <t>session_notes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Activities</t>
+          <t>Session Notes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,48 +589,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>supervisor_signature</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Supervisor Signature</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,53 +646,53 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>supervisor_signature</t>
+          <t>date_submitted</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Supervisor Signature</t>
+          <t>Date Submitted</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>created_by</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date Submitted</t>
+          <t>Created By</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,64 +704,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>created_by</t>
+          <t>assigned_to</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Created By</t>
+          <t>Assigned to</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assigned to</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Submitted by</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>supervisor_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Supervisor Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,64 +796,64 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>supervisee_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submitted by</t>
+          <t>Supervisee Comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>created_date</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Created Date</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>updated_date</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Updated Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>comments2</t>
+          <t>comments_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Comments 2</t>
+          <t>Comments 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,200 +888,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>comments_3</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comments 3</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>comments_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Comments 4</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>comments_5</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Comments 5</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>comments_6</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Comments 6</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>comments_7</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Comments 7</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>comments_8</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Comments 8</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>created_by</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_to</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Assigned to</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +914,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,100 +942,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>activities_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>activities_1</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Activities 1</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>activities_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>activities_2</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Activities 2</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>activities_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>activities_3</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>Activities 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
